--- a/excel_db/assets.xlsx
+++ b/excel_db/assets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -44,6 +44,54 @@
   </si>
   <si>
     <t>created_at</t>
+  </si>
+  <si>
+    <t>purchase_value</t>
+  </si>
+  <si>
+    <t>current_value</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Des/gti/001/26</t>
+  </si>
+  <si>
+    <t>Fan/gti/001/26</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>Fan</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2026-06-07 02:01:06</t>
+  </si>
+  <si>
+    <t>2026-06-07 02:18:54</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>active shape</t>
   </si>
 </sst>
 </file>
@@ -401,10 +449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -434,6 +482,82 @@
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>3000</v>
+      </c>
+      <c r="L2">
+        <v>3000</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <v>350</v>
+      </c>
+      <c r="L3">
+        <v>350</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
